--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/6208-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/6208-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A3CA2AEC-BE4C-49D2-A2BA-436EE89F4637}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C1ADDB8A-E1AB-419C-B1C6-F9DDF39EBE02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{98EBA367-1D97-4B66-84E2-514EC3D30436}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{0A554401-4865-427F-B8E7-43512479D26C}"/>
   </bookViews>
   <sheets>
     <sheet name="6208-dividend-20260225_0_4" sheetId="1" r:id="rId1"/>
@@ -1463,23 +1463,22 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B0FB4C3B-28AD-4F09-BB7A-B556CC303984}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5BC5C58A-7B9D-4F17-837D-7F27AA118632}">
   <dimension ref="A1:R40"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="7.33203125" customWidth="1"/>
-    <col min="3" max="3" width="8.6640625" customWidth="1"/>
-    <col min="4" max="4" width="8.33203125" customWidth="1"/>
-    <col min="5" max="5" width="8" customWidth="1"/>
-    <col min="6" max="10" width="8.33203125" customWidth="1"/>
-    <col min="11" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="8.5546875" customWidth="1"/>
+    <col min="1" max="1" width="6.5" customWidth="1"/>
+    <col min="2" max="2" width="9.25" customWidth="1"/>
+    <col min="3" max="3" width="10.75" customWidth="1"/>
+    <col min="4" max="4" width="10.5" customWidth="1"/>
+    <col min="5" max="5" width="10" customWidth="1"/>
+    <col min="6" max="10" width="10.5" customWidth="1"/>
+    <col min="11" max="13" width="10" customWidth="1"/>
+    <col min="14" max="14" width="10.5" customWidth="1"/>
+    <col min="15" max="18" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
@@ -1507,7 +1506,7 @@
       <c r="Q1" s="31"/>
       <c r="R1" s="23"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="24" t="s">
         <v>1</v>
       </c>
@@ -1537,7 +1536,7 @@
       <c r="Q2" s="33"/>
       <c r="R2" s="34"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="24" t="s">
         <v>2</v>
       </c>
@@ -1583,7 +1582,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="26"/>
       <c r="B4" s="27"/>
       <c r="C4" s="7"/>
@@ -1633,7 +1632,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="38">
         <v>2025</v>
       </c>
@@ -1687,7 +1686,7 @@
         <v>4.26</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
         <v>26</v>
       </c>
@@ -1743,7 +1742,7 @@
         <v>4.26</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="40">
         <v>2024</v>
       </c>
@@ -1797,7 +1796,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="17" t="s">
         <v>26</v>
       </c>
@@ -1853,7 +1852,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="s">
         <v>26</v>
       </c>
@@ -1909,7 +1908,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="38">
         <v>2023</v>
       </c>
@@ -1963,7 +1962,7 @@
         <v>4.88</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
         <v>26</v>
       </c>
@@ -2019,7 +2018,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
         <v>26</v>
       </c>
@@ -2075,7 +2074,7 @@
         <v>4.88</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="40">
         <v>2022</v>
       </c>
@@ -2129,7 +2128,7 @@
         <v>3.95</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="17" t="s">
         <v>26</v>
       </c>
@@ -2185,7 +2184,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="17" t="s">
         <v>26</v>
       </c>
@@ -2241,7 +2240,7 @@
         <v>3.95</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="38">
         <v>2021</v>
       </c>
@@ -2295,7 +2294,7 @@
         <v>4.6100000000000003</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
         <v>26</v>
       </c>
@@ -2351,7 +2350,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
         <v>26</v>
       </c>
@@ -2407,7 +2406,7 @@
         <v>4.6100000000000003</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="40">
         <v>2020</v>
       </c>
@@ -2461,7 +2460,7 @@
         <v>6.22</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="38">
         <v>2019</v>
       </c>
@@ -2515,7 +2514,7 @@
         <v>6.38</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="40">
         <v>2018</v>
       </c>
@@ -2569,7 +2568,7 @@
         <v>4.84</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="38">
         <v>2017</v>
       </c>
@@ -2623,7 +2622,7 @@
         <v>4.29</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="40">
         <v>2016</v>
       </c>
@@ -2677,7 +2676,7 @@
         <v>1.71</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="38">
         <v>2015</v>
       </c>
@@ -2731,7 +2730,7 @@
         <v>6.4</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="40">
         <v>2014</v>
       </c>
@@ -2785,7 +2784,7 @@
         <v>3.23</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="38">
         <v>2013</v>
       </c>
@@ -2839,7 +2838,7 @@
         <v>2.78</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="40">
         <v>2012</v>
       </c>
@@ -2893,7 +2892,7 @@
         <v>12.7</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="38">
         <v>2011</v>
       </c>
@@ -2947,7 +2946,7 @@
         <v>2.65</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="40">
         <v>2010</v>
       </c>
@@ -3001,7 +3000,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="38">
         <v>2009</v>
       </c>
@@ -3055,7 +3054,7 @@
         <v>3.02</v>
       </c>
     </row>
-    <row r="31" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="40">
         <v>2008</v>
       </c>
@@ -3109,7 +3108,7 @@
         <v>7.38</v>
       </c>
     </row>
-    <row r="32" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="38">
         <v>2007</v>
       </c>
@@ -3163,7 +3162,7 @@
         <v>6.49</v>
       </c>
     </row>
-    <row r="33" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="40">
         <v>2006</v>
       </c>
@@ -3217,7 +3216,7 @@
         <v>6.19</v>
       </c>
     </row>
-    <row r="34" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="38">
         <v>2005</v>
       </c>
@@ -3271,7 +3270,7 @@
         <v>7.78</v>
       </c>
     </row>
-    <row r="35" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="40">
         <v>2004</v>
       </c>
@@ -3325,7 +3324,7 @@
         <v>6.14</v>
       </c>
     </row>
-    <row r="36" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="38">
         <v>2003</v>
       </c>
@@ -3379,7 +3378,7 @@
         <v>5.51</v>
       </c>
     </row>
-    <row r="37" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="40">
         <v>2002</v>
       </c>
@@ -3433,7 +3432,7 @@
         <v>2.25</v>
       </c>
     </row>
-    <row r="38" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A38" s="38">
         <v>2001</v>
       </c>
@@ -3487,7 +3486,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="39" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A39" s="40">
         <v>2000</v>
       </c>
@@ -3541,7 +3540,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="40" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A40" s="38" t="s">
         <v>39</v>
       </c>
